--- a/diseases/d032/2000-2004.xlsx
+++ b/diseases/d032/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2001,9 +1995,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2545,9 +2536,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3089,9 +3077,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3633,9 +3618,6 @@
       <c r="O18" t="n">
         <v>1</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -4177,9 +4159,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4721,9 +4700,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -5265,9 +5241,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5809,9 +5782,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6353,9 +6323,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -6897,9 +6864,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7441,9 +7405,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -7589,9 +7550,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -8133,9 +8091,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -8281,9 +8236,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -8825,9 +8777,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -8973,9 +8922,6 @@
       <c r="O48" t="n">
         <v>2</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -9517,9 +9463,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -9665,9 +9608,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -10209,9 +10149,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -10357,9 +10294,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -10901,9 +10835,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -11049,9 +10980,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -11593,9 +11521,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -11741,9 +11666,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -12285,9 +12207,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -12433,9 +12352,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -12977,9 +12893,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -13125,9 +13038,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -13669,9 +13579,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -13817,9 +13724,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -14361,9 +14265,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -14509,9 +14410,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -15053,9 +14951,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -15201,9 +15096,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -15745,9 +15637,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -15893,9 +15782,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -16437,9 +16323,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -16585,9 +16468,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -17129,9 +17009,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -17277,9 +17154,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -17821,9 +17695,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -17969,9 +17840,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -18513,9 +18381,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -18661,9 +18526,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -19205,9 +19067,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -19353,9 +19212,6 @@
       <c r="O108" t="n">
         <v>2</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.04407214257161833</v>
       </c>
@@ -19897,9 +19753,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -20045,9 +19898,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -20589,9 +20439,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -20737,9 +20584,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -21281,9 +21125,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -21429,9 +21270,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -21973,9 +21811,6 @@
       <c r="O123" t="n">
         <v>1</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -22121,9 +21956,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -22665,9 +22497,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -22813,9 +22642,6 @@
       <c r="O128" t="n">
         <v>1</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -23357,9 +23183,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -23505,9 +23328,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -24049,9 +23869,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -24197,9 +24014,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -24741,9 +24555,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -24889,9 +24700,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -25433,9 +25241,6 @@
       <c r="O143" t="n">
         <v>3</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.006313907198255139</v>
       </c>
@@ -25581,9 +25386,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -26125,9 +25927,6 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
@@ -26273,9 +26072,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -26817,9 +26613,6 @@
       <c r="O151" t="n">
         <v>1</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -26965,9 +26758,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -27509,9 +27299,6 @@
       <c r="O155" t="n">
         <v>1</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -27657,9 +27444,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -28201,9 +27985,6 @@
       <c r="O159" t="n">
         <v>3</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.006313907198255139</v>
       </c>
@@ -28349,9 +28130,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -28893,9 +28671,6 @@
       <c r="O163" t="n">
         <v>1</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -29041,9 +28816,6 @@
       <c r="O164" t="n">
         <v>1</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -29585,9 +29357,6 @@
       <c r="O167" t="n">
         <v>4</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.008418542931006853</v>
       </c>
@@ -29733,9 +29502,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -30277,9 +30043,6 @@
       <c r="O171" t="n">
         <v>2</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.004209271465503426</v>
       </c>
@@ -30425,9 +30188,6 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
@@ -30969,9 +30729,6 @@
       <c r="O175" t="n">
         <v>1</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -31117,9 +30874,6 @@
       <c r="O176" t="n">
         <v>2</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -31661,9 +31415,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -31809,9 +31560,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -32353,9 +32101,6 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
@@ -32501,9 +32246,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -33045,9 +32787,6 @@
       <c r="O187" t="n">
         <v>2</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.004193129199294409</v>
       </c>
@@ -33193,9 +32932,6 @@
       <c r="O188" t="n">
         <v>1</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -33737,9 +33473,6 @@
       <c r="O191" t="n">
         <v>1</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -33885,9 +33618,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
@@ -34429,9 +34159,6 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0</v>
       </c>
@@ -34577,9 +34304,6 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
@@ -35121,9 +34845,6 @@
       <c r="O199" t="n">
         <v>3</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0.006289693798941615</v>
       </c>
@@ -35269,9 +34990,6 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -35813,9 +35531,6 @@
       <c r="O203" t="n">
         <v>7</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0.01467595219753043</v>
       </c>
@@ -35961,9 +35676,6 @@
       <c r="O204" t="n">
         <v>0</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0</v>
       </c>
@@ -36505,9 +36217,6 @@
       <c r="O207" t="n">
         <v>8</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.01677251679717764</v>
       </c>
@@ -36653,9 +36362,6 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -37197,9 +36903,6 @@
       <c r="O211" t="n">
         <v>4</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.008386258398588819</v>
       </c>
@@ -37345,9 +37048,6 @@
       <c r="O212" t="n">
         <v>1</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -37889,9 +37589,6 @@
       <c r="O215" t="n">
         <v>2</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.004193129199294409</v>
       </c>
@@ -38037,9 +37734,6 @@
       <c r="O216" t="n">
         <v>0</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0</v>
       </c>
@@ -38581,9 +38275,6 @@
       <c r="O219" t="n">
         <v>7</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0.01467595219753043</v>
       </c>
@@ -38729,9 +38420,6 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0</v>
       </c>
@@ -39273,9 +38961,6 @@
       <c r="O223" t="n">
         <v>6</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.01257938759788323</v>
       </c>
@@ -39421,9 +39106,6 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
@@ -39965,9 +39647,6 @@
       <c r="O227" t="n">
         <v>7</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0.01467595219753043</v>
       </c>
@@ -40111,9 +39790,6 @@
         <v>0</v>
       </c>
       <c r="O228" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q228" t="n">
         <v>0</v>
       </c>
       <c r="R228" t="n">
